--- a/dry_run.xlsx
+++ b/dry_run.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internship Postings'!$A$1:$F$409</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Scan Issues'!$A$1:$E$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Internship Postings'!$A$1:$F$410</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Scan Issues'!$A$1:$E$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F409"/>
+  <dimension ref="A1:F410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4591,27 +4591,27 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>2027 Student Engineer - CPU Design Verification</t>
+          <t>Mechanical Drafter</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Pelican Energy Consultants</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>https://careers.amd.com/careers-home/jobs/94274?lang=en-us</t>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=9ecaf208-0ecb-4b01-a7fe-60095fa096a4&amp;ccId=9203505775391_3&amp;jobId=9205502861538_1&amp;lang=en_US</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Location US,CA,San Jose 2100 Logic Drive San Jose, California US</t>
+          <t>Covington, LA</t>
         </is>
       </c>
     </row>
@@ -4621,27 +4621,27 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Reasonable Accommodation and Drug Free Workplace policyLearn more (Opens in a new window)</t>
+          <t>Entry Level Mechanical Engineer</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Pelican Energy Consultants</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>https://www.apple.com/careers/us/accommodation_drugfree.html</t>
+          <t>https://workforcenow.adp.com/mascsr/default/mdf/recruitment/recruitment.html?cid=9ecaf208-0ecb-4b01-a7fe-60095fa096a4&amp;ccId=9203505775391_3&amp;jobId=9205502851594_1&amp;lang=en_US</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Covington, LA</t>
         </is>
       </c>
     </row>
@@ -4651,17 +4651,17 @@
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>2027 Student Engineer - CPU Design Verification</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>AprilAire</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aprilaire.com/jobs/2487?lang=en-us</t>
+          <t>https://careers.amd.com/careers-home/jobs/94274?lang=en-us</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Location Sun Prairie, Wisconsin</t>
+          <t>Location US,CA,San Jose 2100 Logic Drive San Jose, California US</t>
         </is>
       </c>
     </row>
@@ -4681,17 +4681,17 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineer I</t>
+          <t>Reasonable Accommodation and Drug Free Workplace policyLearn more (Opens in a new window)</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>AprilAire</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>https://careers.aprilaire.com/jobs/2651?lang=en-us</t>
+          <t>https://www.apple.com/careers/us/accommodation_drugfree.html</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Location Sun Prairie, Wisconsin</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Principal Automation Engineer</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>https://careers.aprilaire.com/jobs/2599?lang=en-us</t>
+          <t>https://careers.aprilaire.com/jobs/2487?lang=en-us</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Mechanical Engineer I</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>https://careers.aprilaire.com/jobs/2590?lang=en-us</t>
+          <t>https://careers.aprilaire.com/jobs/2651?lang=en-us</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -4771,17 +4771,17 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Junior Mechanical Engineer</t>
+          <t>Principal Automation Engineer</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Atlas Copco</t>
+          <t>AprilAire</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>https://www.jobs.atlascopcogroup.com/job/Junior-Mechanical-Engineer/175865-en_US</t>
+          <t>https://careers.aprilaire.com/jobs/2599?lang=en-us</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Location Sun Prairie, Wisconsin</t>
         </is>
       </c>
     </row>
@@ -4801,17 +4801,17 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>Project Engineer - Aftermarket Engineering</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Atlas Copco</t>
+          <t>AprilAire</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>https://www.jobs.atlascopcogroup.com/job/Project-Engineer-Aftermarket-Engineering/175742-en_US</t>
+          <t>https://careers.aprilaire.com/jobs/2590?lang=en-us</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
@@ -4821,7 +4821,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Location Sun Prairie, Wisconsin</t>
         </is>
       </c>
     </row>
@@ -4831,17 +4831,17 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>Junior Mechanical Engineer</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>ATS Automation</t>
+          <t>Atlas Copco</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.atsautomation.com/PA/job/Lewis-Center-Automation-Engineer-OH-43035-9445/1408454133/</t>
+          <t>https://www.jobs.atlascopcogroup.com/job/Junior-Mechanical-Engineer/175865-en_US</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -4861,17 +4861,17 @@
       </c>
       <c r="B145" s="4" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>Project Engineer - Aftermarket Engineering</t>
         </is>
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>ATS Automation</t>
+          <t>Atlas Copco</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.atsautomation.com/PA/job/Raleigh-Automation-Engineer-NC-27603/1371671333/</t>
+          <t>https://www.jobs.atlascopcogroup.com/job/Project-Engineer-Aftermarket-Engineering/175742-en_US</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Automation Engineer (m/f/d)</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.atsautomation.com/PA/job/Dublin-Automation-Engineer-%28mfd%29-L-D11-TK4C/1391422333/</t>
+          <t>https://jobs.atsautomation.com/PA/job/Lewis-Center-Automation-Engineer-OH-43035-9445/1408454133/</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="B147" s="4" t="inlineStr">
         <is>
-          <t>Global Manager, Mechanical Design Manufacturing Solutions</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="C147" s="4" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.atsautomation.com/job/Cambridge-Global-Manager%2C-Mechanical-Design-Manufacturing-Solutions-ON-N3H-4R7/1446200533/</t>
+          <t>https://jobs.atsautomation.com/PA/job/Raleigh-Automation-Engineer-NC-27603/1371671333/</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
@@ -4951,7 +4951,7 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Group Lead, Mechanical Assembly</t>
+          <t>Automation Engineer (m/f/d)</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.atsautomation.com/job/Cambridge-Group-Lead%2C-Mechanical-Assembly-ON-N3H-4R7/1448522633/</t>
+          <t>https://jobs.atsautomation.com/PA/job/Dublin-Automation-Engineer-%28mfd%29-L-D11-TK4C/1391422333/</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>Junior Mechanical Designer</t>
+          <t>Global Manager, Mechanical Design Manufacturing Solutions</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.atsautomation.com/job/Cambridge-Junior-Mechanical-Designer-ON-N3H-4R7/1447329533/</t>
+          <t>https://jobs.atsautomation.com/job/Cambridge-Global-Manager%2C-Mechanical-Design-Manufacturing-Solutions-ON-N3H-4R7/1446200533/</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Junior Systems Design Engineer I</t>
+          <t>Group Lead, Mechanical Assembly</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.atsautomation.com/job/Lewis-Center-Junior-Systems-Design-Engineer-I-OH-43035-9445/1447299933/</t>
+          <t>https://jobs.atsautomation.com/job/Cambridge-Group-Lead%2C-Mechanical-Assembly-ON-N3H-4R7/1448522633/</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering</t>
+          <t>Junior Mechanical Designer</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.atsautomation.com/job/Pocomoke-Manufacturing-Engineering-MD-21851/1449532033/</t>
+          <t>https://jobs.atsautomation.com/job/Cambridge-Junior-Mechanical-Designer-ON-N3H-4R7/1447329533/</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Design Manager</t>
+          <t>Junior Systems Design Engineer I</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.atsautomation.com/job/Cambridge-Mechanical-Design-Manager-ON-N3H-4R7/1449616833/</t>
+          <t>https://jobs.atsautomation.com/job/Lewis-Center-Junior-Systems-Design-Engineer-I-OH-43035-9445/1447299933/</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Manufacturing Engineering</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.atsautomation.com/PA/job/Lewis-Center-Senior-Automation-Engineer-OH-43035-9445/1408527433/</t>
+          <t>https://jobs.atsautomation.com/job/Pocomoke-Manufacturing-Engineering-MD-21851/1449532033/</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Mechanical Design Manager</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.atsautomation.com/PA/job/Guaynabo-Senior-Automation-Engineer-PR-00968-8058/1249247601/</t>
+          <t>https://jobs.atsautomation.com/job/Cambridge-Mechanical-Design-Manager-ON-N3H-4R7/1449616833/</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>Senior Mechanical Designer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.atsautomation.com/job/Cambridge-Senior-Mechanical-Designer-ON-N3H-4R7/1447333533/</t>
+          <t>https://jobs.atsautomation.com/PA/job/Lewis-Center-Senior-Automation-Engineer-OH-43035-9445/1408527433/</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Senior Mechanical Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.atsautomation.com/job/Cambridge-Senior-Mechanical-Engineer-ON-N3H-4R7/1437342233/</t>
+          <t>https://jobs.atsautomation.com/PA/job/Guaynabo-Senior-Automation-Engineer-PR-00968-8058/1249247601/</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="B157" s="4" t="inlineStr">
         <is>
-          <t>Senior Mechanical Engineer</t>
+          <t>Senior Mechanical Designer</t>
         </is>
       </c>
       <c r="C157" s="4" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="D157" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.atsautomation.com/job/Lewis-Center-Senior-Mechanical-Engineer-OH-43035-9445/1227166101/</t>
+          <t>https://jobs.atsautomation.com/job/Cambridge-Senior-Mechanical-Designer-ON-N3H-4R7/1447333533/</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Senior Mechanical Engineer</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.atsautomation.com/job/Cambridge-Senior-Systems-Engineer-ON-N3H-4R7/1439822433/</t>
+          <t>https://jobs.atsautomation.com/job/Cambridge-Senior-Mechanical-Engineer-ON-N3H-4R7/1437342233/</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer</t>
+          <t>Senior Mechanical Engineer</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.atsautomation.com/PA/job/Indianapolis-Systems-Engineer-IN-46250/1420951533/</t>
+          <t>https://jobs.atsautomation.com/job/Lewis-Center-Senior-Mechanical-Engineer-OH-43035-9445/1227166101/</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
@@ -5311,17 +5311,17 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Control Systems Engineer</t>
+          <t>Senior Systems Engineer</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Audubon</t>
+          <t>ATS Automation</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001185359910</t>
+          <t>https://jobs.atsautomation.com/job/Cambridge-Senior-Systems-Engineer-ON-N3H-4R7/1439822433/</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Metairie, LA, USA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -5341,17 +5341,17 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>Control Systems Engineer, Senior</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Audubon</t>
+          <t>ATS Automation</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001185357106</t>
+          <t>https://jobs.atsautomation.com/PA/job/Indianapolis-Systems-Engineer-IN-46250/1420951533/</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Metairie, LA, USA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5371,7 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Control Systems Engineering Specialist</t>
+          <t>Control Systems Engineer</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001212045606</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001185359910</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Houston, TX, USA</t>
+          <t>Metairie, LA, USA</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineer</t>
+          <t>Control Systems Engineer, Senior</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001220995706</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001185357106</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>Houston, TX, USA</t>
+          <t>Metairie, LA, USA</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineer, Principal</t>
+          <t>Control Systems Engineering Specialist</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001153073006</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001212045606</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineer, Senior</t>
+          <t>Mechanical Engineer</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001102604400</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001220995706</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>Metairie, LA, USA</t>
+          <t>Houston, TX, USA</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineer, Senior (Temporary)</t>
+          <t>Mechanical Engineer, Principal</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001209074506</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001153073006</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>Metairie, LA, USA</t>
+          <t>Houston, TX, USA</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Associate I</t>
+          <t>Mechanical Engineer, Senior</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001216070206</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001102604400</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Associate I</t>
+          <t>Mechanical Engineer, Senior (Temporary)</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001214497100</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001209074506</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Houston, TX, USA</t>
+          <t>Metairie, LA, USA</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001188120206</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001216070206</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>Houston, TX, USA</t>
+          <t>Metairie, LA, USA</t>
         </is>
       </c>
     </row>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001155921806</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001214497100</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Associate, Principal</t>
+          <t>Mechanical Engineering Associate I</t>
         </is>
       </c>
       <c r="C171" s="4" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001152894606</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001188120206</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Associate, Senior</t>
+          <t>Mechanical Engineering Associate I</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001194348806</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001155921806</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>Metairie, LA, USA</t>
+          <t>Houston, TX, USA</t>
         </is>
       </c>
     </row>
@@ -5701,7 +5701,7 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Associate, Senior</t>
+          <t>Mechanical Engineering Associate, Principal</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001087034306</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001152894606</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Associate, Sr</t>
+          <t>Mechanical Engineering Associate, Senior</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001230936106</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001194348806</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>Houston, TX, USA</t>
+          <t>Metairie, LA, USA</t>
         </is>
       </c>
     </row>
@@ -5761,7 +5761,7 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Specialist, Senior</t>
+          <t>Mechanical Engineering Associate, Senior</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001197911206</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001087034306</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Supervisor - Offshore</t>
+          <t>Mechanical Engineering Associate, Sr</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001167941406</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001230936106</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>Process Engineer, Principal</t>
+          <t>Mechanical Engineering Specialist, Senior</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001193403006</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001197911206</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Process Engineer, Senior</t>
+          <t>Mechanical Engineering Supervisor - Offshore</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001205810406</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001167941406</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Process Engineer, Senior</t>
+          <t>Process Engineer, Principal</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001140878606</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001193403006</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>Metairie, LA, USA</t>
+          <t>Houston, TX, USA</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Process Engineering Associate I</t>
+          <t>Process Engineer, Senior</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001168017806</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001205810406</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Process Engineering Associate III</t>
+          <t>Process Engineer, Senior</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="D181" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001136040206</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001140878606</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Houston, TX, USA</t>
+          <t>Metairie, LA, USA</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Process Engineering Associate IV</t>
+          <t>Process Engineering Associate I</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001150940406</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001168017806</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>Process Engineering Associate III</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="D183" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001194906206</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001136040206</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>Henning, IL, USA</t>
+          <t>Houston, TX, USA</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6031,7 @@
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>Process Engineering Associate IV</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001177362806</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001150940406</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="D185" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001141752006</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001194906206</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Houston, TX, USA</t>
+          <t>Henning, IL, USA</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Project Engineer I</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001219167506</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001177362806</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Project Engineer III</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001219171506</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001141752006</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer</t>
+          <t>Project Engineer I</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001198013300</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001219167506</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>Canonsburg, PA, USA</t>
+          <t>Houston, TX, USA</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Senior Mechanical Engineer</t>
+          <t>Project Engineer III</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="D189" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001150863000</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001219171506</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Tulsa, OK, USA</t>
+          <t>Houston, TX, USA</t>
         </is>
       </c>
     </row>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Senior Mechanical Engineer</t>
+          <t>Senior Automation Engineer</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001127305406</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001198013300</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>Houston, TX, USA</t>
+          <t>Canonsburg, PA, USA</t>
         </is>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Senior Project Engineer</t>
+          <t>Senior Mechanical Engineer</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="D191" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001183413106</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001150863000</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>Houston, TX, USA</t>
+          <t>Tulsa, OK, USA</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Sr. Process Engineer</t>
+          <t>Senior Mechanical Engineer</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001226421806</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001127305406</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Sr. Process Engineer</t>
+          <t>Senior Project Engineer</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001220954406</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001183413106</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Sr. Project Engineer</t>
+          <t>Sr. Process Engineer</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001229519406</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001226421806</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>Canonsburg, PA, USA</t>
+          <t>Houston, TX, USA</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6361,7 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Structural Engineer</t>
+          <t>Sr. Process Engineer</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="D195" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001221013906</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001220954406</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Structural Engineer</t>
+          <t>Sr. Project Engineer</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001174906606</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001229519406</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Houston, TX, USA</t>
+          <t>Canonsburg, PA, USA</t>
         </is>
       </c>
     </row>
@@ -6421,17 +6421,17 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Facilities Engineer</t>
+          <t>Structural Engineer</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Audubon</t>
         </is>
       </c>
       <c r="D197" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.bosch.com/en/job/REF296685Q-facilities-engineer</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001221013906</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Houston, TX, USA</t>
         </is>
       </c>
     </row>
@@ -6451,17 +6451,17 @@
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>HVAC Branch/Store Manager Spring, TX</t>
+          <t>Structural Engineer</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>Audubon</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.bosch.com/en/job/REF1369U-hvac-branch-store-manager-spring-tx</t>
+          <t>https://myjobs.adp.com/auduboncorporatecareers/cx/job-details?reqId=5001174906606</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Houston, TX, USA</t>
         </is>
       </c>
     </row>
@@ -6481,17 +6481,17 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineer - Automated Assembly</t>
+          <t>Vice President, Strategy &amp; New Business Development</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.bosch.com/en/job/REF297118R-manufacturing-engineer-automated-assembly</t>
+          <t>https://jobs.bd.com/en/job/tempe/vice-president-strategy-and-new-business-development/159/102579178304</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Tempe, AZ</t>
         </is>
       </c>
     </row>
@@ -6511,7 +6511,7 @@
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Assembler - Linear Technologies</t>
+          <t>Facilities Engineer</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.bosch.com/en/job/REF297106Z-mechanical-assembler-linear-technologies</t>
+          <t>https://jobs.bosch.com/en/job/REF296685Q-facilities-engineer</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Product Engineer</t>
+          <t>HVAC Branch/Store Manager Spring, TX</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="D201" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.bosch.com/en/job/REF296922S-mechanical-product-engineer</t>
+          <t>https://jobs.bosch.com/en/job/REF1369U-hvac-branch-store-manager-spring-tx</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
@@ -6571,17 +6571,17 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Electronic Systems - Summer... (1)</t>
+          <t>Manufacturing Engineer - Automated Assembly</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>https://cummins.jobs/job-titles/electronic-systems-summer-internship-positions/jobs/?location=united+states&amp;q=intern</t>
+          <t>https://jobs.bosch.com/en/job/REF297118R-manufacturing-engineer-automated-assembly</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Thermal and Fluid Systems EngineerColumbus, INWork Type: On-site with Flexibility</t>
+          <t>Mechanical Assembler - Linear Technologies</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
         <is>
-          <t>https://cummins.jobs/columbus-in/thermal-and-fluid-systems-engineer/189ED54BAFCC44B591BA0BF80E10B45A/job/</t>
+          <t>https://jobs.bosch.com/en/job/REF297106Z-mechanical-assembler-linear-technologies</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
@@ -6631,17 +6631,17 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineer in Training 1</t>
+          <t>Mechanical Product Engineer</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>EwingCole</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4577924</t>
+          <t>https://jobs.bosch.com/en/job/REF296922S-mechanical-product-engineer</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineer in Training 1</t>
+          <t>Electronic Systems - Summer... (1)</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>EwingCole</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4455594</t>
+          <t>https://cummins.jobs/job-titles/electronic-systems-summer-internship-positions/jobs/?location=united+states&amp;q=intern</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
@@ -6691,17 +6691,17 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Project Engineer</t>
+          <t>Thermal and Fluid Systems EngineerColumbus, INWork Type: On-site with Flexibility</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>EwingCole</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4577901</t>
+          <t>https://cummins.jobs/columbus-in/thermal-and-fluid-systems-engineer/189ED54BAFCC44B591BA0BF80E10B45A/job/</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Plumbing Project Engineer</t>
+          <t>Mechanical Engineer in Training 1</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="D207" s="5" t="inlineStr">
         <is>
-          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4349068</t>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4577924</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Senior Mechanical Project Engineer</t>
+          <t>Mechanical Engineer in Training 1</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4543843</t>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4455594</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Senior Mechanical Project Engineer</t>
+          <t>Mechanical Project Engineer</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="D209" s="5" t="inlineStr">
         <is>
-          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4220312</t>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4577901</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Senior Mechanical Project Engineer</t>
+          <t>Plumbing Project Engineer</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4194532</t>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4349068</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Structural Engineer in Training 1</t>
+          <t>Senior Mechanical Project Engineer</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="D211" s="5" t="inlineStr">
         <is>
-          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4513332</t>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4543843</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Structural Project Engineer</t>
+          <t>Senior Mechanical Project Engineer</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4182467</t>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4220312</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Structural Project Engineer</t>
+          <t>Senior Mechanical Project Engineer</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="D213" s="5" t="inlineStr">
         <is>
-          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4268027</t>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4194532</t>
         </is>
       </c>
       <c r="E213" s="4" t="inlineStr">
@@ -6931,17 +6931,17 @@
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>3D Print Optimization Engineer - June 2027 New Grads</t>
+          <t>Structural Engineer in Training 1</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Formlabs</t>
+          <t>EwingCole</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8331440/apply/</t>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4513332</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -6961,17 +6961,17 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>3D Print Optimization Engineer - June 2027 New Grads</t>
+          <t>Structural Project Engineer</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Formlabs</t>
+          <t>EwingCole</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8331442/apply/</t>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4182467</t>
         </is>
       </c>
       <c r="E215" s="4" t="inlineStr">
@@ -6991,17 +6991,17 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Field Service Engineer - Newark</t>
+          <t>Structural Project Engineer</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Formlabs</t>
+          <t>EwingCole</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8214416/apply/</t>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4268027</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Field Service Technician - Newark</t>
+          <t>3D Print Optimization Engineer - June 2027 New Grads</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8076134/apply/</t>
+          <t>https://careers.formlabs.com/job/8331440/apply/</t>
         </is>
       </c>
       <c r="E217" s="4" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment Coordinator - May 2027 Graduates</t>
+          <t>3D Print Optimization Engineer - June 2027 New Grads</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8249635/apply/</t>
+          <t>https://careers.formlabs.com/job/8331442/apply/</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Head of Manufacturing Engineering</t>
+          <t>Field Service Engineer - Newark</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="D219" s="5" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8203847/apply/</t>
+          <t>https://careers.formlabs.com/job/8214416/apply/</t>
         </is>
       </c>
       <c r="E219" s="4" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Makerspace Fellow (Winter/Spring 2027)</t>
+          <t>Field Service Technician - Newark</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8328598/apply/</t>
+          <t>https://careers.formlabs.com/job/8076134/apply/</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Makerspace Fellow (Winter/Spring 2027)</t>
+          <t>Fulfillment Coordinator - May 2027 Graduates</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -7151,7 +7151,7 @@
       </c>
       <c r="D221" s="5" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8315981/apply/</t>
+          <t>https://careers.formlabs.com/job/8249635/apply/</t>
         </is>
       </c>
       <c r="E221" s="4" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing Engineer</t>
+          <t>Head of Manufacturing Engineering</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8249899/apply/</t>
+          <t>https://careers.formlabs.com/job/8203847/apply/</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="B223" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineer - May 2027 Graduates</t>
+          <t>Makerspace Fellow (Winter/Spring 2027)</t>
         </is>
       </c>
       <c r="C223" s="4" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="D223" s="5" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8250319/apply/</t>
+          <t>https://careers.formlabs.com/job/8328598/apply/</t>
         </is>
       </c>
       <c r="E223" s="4" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing Test Engineer</t>
+          <t>Makerspace Fellow (Winter/Spring 2027)</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="D224" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8318822/apply/</t>
+          <t>https://careers.formlabs.com/job/8315981/apply/</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Materials Scientist - June 2027 Grads</t>
+          <t>Manufacturing Engineer</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="D225" s="5" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8241539/apply/</t>
+          <t>https://careers.formlabs.com/job/8249899/apply/</t>
         </is>
       </c>
       <c r="E225" s="4" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Materials Scientist - June 2027 Grads</t>
+          <t>Manufacturing Engineer - May 2027 Graduates</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="D226" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8241540/apply/</t>
+          <t>https://careers.formlabs.com/job/8250319/apply/</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineer</t>
+          <t>Manufacturing Test Engineer</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="D227" s="5" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8241493/apply/</t>
+          <t>https://careers.formlabs.com/job/8318822/apply/</t>
         </is>
       </c>
       <c r="E227" s="4" t="inlineStr">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineer</t>
+          <t>Materials Scientist - June 2027 Grads</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="D228" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8317876/apply/</t>
+          <t>https://careers.formlabs.com/job/8241539/apply/</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineer - December 2026 &amp; May 2027 Graduates</t>
+          <t>Materials Scientist - June 2027 Grads</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="D229" s="5" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8221092/apply/</t>
+          <t>https://careers.formlabs.com/job/8241540/apply/</t>
         </is>
       </c>
       <c r="E229" s="4" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineer - Shenzhen</t>
+          <t>Mechanical Engineer</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="D230" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/5825194/apply/</t>
+          <t>https://careers.formlabs.com/job/8241493/apply/</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineering Manager</t>
+          <t>Mechanical Engineer</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="D231" s="5" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8237436/apply/</t>
+          <t>https://careers.formlabs.com/job/8317876/apply/</t>
         </is>
       </c>
       <c r="E231" s="4" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Project Manager</t>
+          <t>Mechanical Engineer - December 2026 &amp; May 2027 Graduates</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="D232" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8221617/apply/</t>
+          <t>https://careers.formlabs.com/job/8221092/apply/</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Process Engineer</t>
+          <t>Mechanical Engineer - Shenzhen</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="D233" s="5" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/6814095/apply/</t>
+          <t>https://careers.formlabs.com/job/5825194/apply/</t>
         </is>
       </c>
       <c r="E233" s="4" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Mechanical Engineering Manager</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="D234" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/7159633/apply/</t>
+          <t>https://careers.formlabs.com/job/8237436/apply/</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>R&amp;D Engineer</t>
+          <t>Mechanical Project Manager</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="D235" s="5" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8249038/apply/</t>
+          <t>https://careers.formlabs.com/job/8221617/apply/</t>
         </is>
       </c>
       <c r="E235" s="4" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>R&amp;D Reliability/Test Engineer</t>
+          <t>Process Engineer</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="D236" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8241460/apply/</t>
+          <t>https://careers.formlabs.com/job/6814095/apply/</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>R&amp;D Reliability/Test Engineer</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="D237" s="5" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8241461/apply/</t>
+          <t>https://careers.formlabs.com/job/7159633/apply/</t>
         </is>
       </c>
       <c r="E237" s="4" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>R&amp;D Reliability/Test Engineer - June 2027 Grads</t>
+          <t>R&amp;D Engineer</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="D238" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8241465/apply/</t>
+          <t>https://careers.formlabs.com/job/8249038/apply/</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>R&amp;D Reliability/Test Engineer - June 2027 Grads</t>
+          <t>R&amp;D Reliability/Test Engineer</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="D239" s="5" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8241472/apply/</t>
+          <t>https://careers.formlabs.com/job/8241460/apply/</t>
         </is>
       </c>
       <c r="E239" s="4" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Senior 3D Printing R&amp;D Engineer</t>
+          <t>R&amp;D Reliability/Test Engineer</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="D240" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8249055/apply/</t>
+          <t>https://careers.formlabs.com/job/8241461/apply/</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Senior Advanced Manufacturing Engineer</t>
+          <t>R&amp;D Reliability/Test Engineer - June 2027 Grads</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="D241" s="5" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8329544/apply/</t>
+          <t>https://careers.formlabs.com/job/8241465/apply/</t>
         </is>
       </c>
       <c r="E241" s="4" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Senior Mechanical Engineer</t>
+          <t>R&amp;D Reliability/Test Engineer - June 2027 Grads</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="D242" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8241500/apply/</t>
+          <t>https://careers.formlabs.com/job/8241472/apply/</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Senior Product Design Engineer</t>
+          <t>Senior 3D Printing R&amp;D Engineer</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="D243" s="5" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8249058/apply/</t>
+          <t>https://careers.formlabs.com/job/8249055/apply/</t>
         </is>
       </c>
       <c r="E243" s="4" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Senior R&amp;D Reliability/Test Engineer</t>
+          <t>Senior Advanced Manufacturing Engineer</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="D244" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8311915/apply/</t>
+          <t>https://careers.formlabs.com/job/8329544/apply/</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Senior UX/UI Product Designer</t>
+          <t>Senior Mechanical Engineer</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="D245" s="5" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8223131/apply/</t>
+          <t>https://careers.formlabs.com/job/8241500/apply/</t>
         </is>
       </c>
       <c r="E245" s="4" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>SLS Materials Scientist - June 2027 Grads</t>
+          <t>Senior Product Design Engineer</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="D246" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8241541/apply/</t>
+          <t>https://careers.formlabs.com/job/8249058/apply/</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>SLS Materials Scientist - June 2027 Grads</t>
+          <t>Senior R&amp;D Reliability/Test Engineer</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="D247" s="5" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8241542/apply/</t>
+          <t>https://careers.formlabs.com/job/8311915/apply/</t>
         </is>
       </c>
       <c r="E247" s="4" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Test Tooling Engineer</t>
+          <t>Senior UX/UI Product Designer</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="D248" s="3" t="inlineStr">
         <is>
-          <t>https://careers.formlabs.com/job/8237289/apply/</t>
+          <t>https://careers.formlabs.com/job/8223131/apply/</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -7981,17 +7981,17 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Controls Systems Engineering Supervisor</t>
+          <t>SLS Materials Scientist - June 2027 Grads</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Hendrickson</t>
+          <t>Formlabs</t>
         </is>
       </c>
       <c r="D249" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001177429906</t>
+          <t>https://careers.formlabs.com/job/8241541/apply/</t>
         </is>
       </c>
       <c r="E249" s="4" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>North Canton, OH, USA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -8011,17 +8011,17 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing Engineer</t>
+          <t>SLS Materials Scientist - June 2027 Grads</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Hendrickson</t>
+          <t>Formlabs</t>
         </is>
       </c>
       <c r="D250" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001231466806</t>
+          <t>https://careers.formlabs.com/job/8241542/apply/</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, USA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -8041,17 +8041,17 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineer</t>
+          <t>Test Tooling Engineer</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Hendrickson</t>
+          <t>Formlabs</t>
         </is>
       </c>
       <c r="D251" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001231173206</t>
+          <t>https://careers.formlabs.com/job/8237289/apply/</t>
         </is>
       </c>
       <c r="E251" s="4" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>Hebron, OH, USA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8071,7 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing Engineer</t>
+          <t>Controls Systems Engineering Supervisor</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="D252" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001213709506</t>
+          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001177429906</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>Lebanon, IN, USA</t>
+          <t>North Canton, OH, USA</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineer (P1)</t>
+          <t>Manufacturing Engineer</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="D253" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001220440906</t>
+          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001231466806</t>
         </is>
       </c>
       <c r="E253" s="4" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>Kendallville, IN, USA</t>
+          <t>Chattanooga, TN, USA</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing Engineer II</t>
+          <t>Manufacturing Engineer</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="D254" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001175404106</t>
+          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001231173206</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>Crest Hill, IL, USA</t>
+          <t>Hebron, OH, USA</t>
         </is>
       </c>
     </row>
@@ -8161,7 +8161,7 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Tech</t>
+          <t>Manufacturing Engineer</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="D255" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001214863806</t>
+          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001213709506</t>
         </is>
       </c>
       <c r="E255" s="4" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>Lebanon, KY, USA</t>
+          <t>Lebanon, IN, USA</t>
         </is>
       </c>
     </row>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Tech II</t>
+          <t>Manufacturing Engineer (P1)</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="D256" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001211773106</t>
+          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001220440906</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>Somerset, KY, USA</t>
+          <t>Kendallville, IN, USA</t>
         </is>
       </c>
     </row>
@@ -8221,7 +8221,7 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Technician (3rd Shift)</t>
+          <t>Manufacturing Engineer II</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D257" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001208926906</t>
+          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001175404106</t>
         </is>
       </c>
       <c r="E257" s="4" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>Lebanon, IN, USA</t>
+          <t>Crest Hill, IL, USA</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Technician - 2nd Shift</t>
+          <t>Manufacturing Engineering Tech</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="D258" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001213620506</t>
+          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001214863806</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>North Canton, OH, USA</t>
+          <t>Lebanon, KY, USA</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Technician - Afternoons</t>
+          <t>Manufacturing Engineering Tech II</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="D259" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001232395306</t>
+          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001211773106</t>
         </is>
       </c>
       <c r="E259" s="4" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>Navarre, OH, USA</t>
+          <t>Somerset, KY, USA</t>
         </is>
       </c>
     </row>
@@ -8311,7 +8311,7 @@
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing Engineering Technician II - Night Shift</t>
+          <t>Manufacturing Engineering Technician (3rd Shift)</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="D260" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001222109306</t>
+          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001208926906</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>Navarre, OH, USA</t>
+          <t>Lebanon, IN, USA</t>
         </is>
       </c>
     </row>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>Manufacturing Engineering Technician - 2nd Shift</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
@@ -8351,7 +8351,7 @@
       </c>
       <c r="D261" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001176402606</t>
+          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001213620506</t>
         </is>
       </c>
       <c r="E261" s="4" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>Medina, NY, USA</t>
+          <t>North Canton, OH, USA</t>
         </is>
       </c>
     </row>
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Manufacturing Engineering Technician - Afternoons</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="D262" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001226058606</t>
+          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001232395306</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -8391,7 +8391,7 @@
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>Canton, OH, USA</t>
+          <t>Navarre, OH, USA</t>
         </is>
       </c>
     </row>
@@ -8401,7 +8401,7 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Manufacturing Engineering Technician II - Night Shift</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="D263" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001207754806</t>
+          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001222109306</t>
         </is>
       </c>
       <c r="E263" s="4" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>Lebanon, KY, USA</t>
+          <t>Navarre, OH, USA</t>
         </is>
       </c>
     </row>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Senior Project Engineer</t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="D264" s="3" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001220425906</t>
+          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001176402606</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>Woodridge, IL, USA</t>
+          <t>Medina, NY, USA</t>
         </is>
       </c>
     </row>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Welding Process Engineer II</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="D265" s="5" t="inlineStr">
         <is>
-          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001166529406</t>
+          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001226058606</t>
         </is>
       </c>
       <c r="E265" s="4" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>Lebanon, KY, USA</t>
+          <t>Canton, OH, USA</t>
         </is>
       </c>
     </row>
@@ -8491,17 +8491,17 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>ADAS Driving Validation Engineer</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Hyundai</t>
+          <t>Hendrickson</t>
         </is>
       </c>
       <c r="D266" s="3" t="inlineStr">
         <is>
-          <t>https://careers-americas.hyundai.com/hatci/job/Superior-Charter-Township-ADAS-Driving-Validation-Engineer-MI-48198/1439371200/</t>
+          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001207754806</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Lebanon, KY, USA</t>
         </is>
       </c>
     </row>
@@ -8521,17 +8521,17 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Battery Engineering Design - Design Engineer I/II</t>
+          <t>Senior Project Engineer</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Hyundai</t>
+          <t>Hendrickson</t>
         </is>
       </c>
       <c r="D267" s="5" t="inlineStr">
         <is>
-          <t>https://careers-americas.hyundai.com/hatci/job/superior-township-Battery-Engineering-Design-Design-Engineer-III-MI-48198/1439333600/</t>
+          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001220425906</t>
         </is>
       </c>
       <c r="E267" s="4" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Woodridge, IL, USA</t>
         </is>
       </c>
     </row>
@@ -8551,17 +8551,17 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Mechanical Engineer/Designer (HVAC Systems Design) Charlotte, NC →</t>
+          <t>Welding Process Engineer II</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Jordan &amp; Skala Engineers</t>
+          <t>Hendrickson</t>
         </is>
       </c>
       <c r="D268" s="3" t="inlineStr">
         <is>
-          <t>https://jordanskala.com/job/mechanical-engineer-designer-hvac-systems-design/</t>
+          <t>https://myjobs.adp.com/hendrickson/cx/job-details?reqId=5001166529406</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>Charlotte, NC</t>
+          <t>Lebanon, KY, USA</t>
         </is>
       </c>
     </row>
@@ -8581,17 +8581,17 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Mechanical Engineer/Designer (HVAC Systems Design) Norcross, GA →</t>
+          <t>ADAS Driving Validation Engineer</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Jordan &amp; Skala Engineers</t>
+          <t>Hyundai</t>
         </is>
       </c>
       <c r="D269" s="5" t="inlineStr">
         <is>
-          <t>https://jordanskala.com/job/mechanical-engineer-designer-hvac-systems-design-2/</t>
+          <t>https://careers-americas.hyundai.com/hatci/job/Superior-Charter-Township-ADAS-Driving-Validation-Engineer-MI-48198/1439371200/</t>
         </is>
       </c>
       <c r="E269" s="4" t="inlineStr">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>Norcross, GA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -8611,17 +8611,17 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Design Engineer</t>
+          <t>Battery Engineering Design - Design Engineer I/II</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>JTEKT North America</t>
+          <t>Hyundai</t>
         </is>
       </c>
       <c r="D270" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20848</t>
+          <t>https://careers-americas.hyundai.com/hatci/job/superior-township-Battery-Engineering-Design-Design-Engineer-III-MI-48198/1439333600/</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineer</t>
+          <t>Design Engineer</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="D271" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20780</t>
+          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20848</t>
         </is>
       </c>
       <c r="E271" s="4" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="D272" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20316</t>
+          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20780</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Production Engineer (Controls focused)</t>
+          <t>Manufacturing Engineer</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="D273" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20375</t>
+          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20316</t>
         </is>
       </c>
       <c r="E273" s="4" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Production Engineer (machining focused)</t>
+          <t>Production Engineer (Controls focused)</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="D274" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20715</t>
+          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20375</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Project Engineer - SYL</t>
+          <t>Production Engineer (machining focused)</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="D275" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20099</t>
+          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20715</t>
         </is>
       </c>
       <c r="E275" s="4" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Project Engineer - SYL</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="D276" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/19746</t>
+          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20099</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Quality Engineer - VON</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="D277" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20955</t>
+          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/19746</t>
         </is>
       </c>
       <c r="E277" s="4" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Senior Product Design Engineer</t>
+          <t>Quality Engineer - VON</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="D278" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20918</t>
+          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20955</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Senior Production Engineer</t>
+          <t>Senior Product Design Engineer</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="D279" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20710</t>
+          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20918</t>
         </is>
       </c>
       <c r="E279" s="4" t="inlineStr">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Senior Turning Manufacturing Engineer</t>
+          <t>Senior Production Engineer</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="D280" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20059</t>
+          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20710</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Project Engineer</t>
+          <t>Senior Turning Manufacturing Engineer</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Legence</t>
+          <t>JTEKT North America</t>
         </is>
       </c>
       <c r="D281" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.dayforcehcm.com/en-US/legence/studentportal/jobs/33975</t>
+          <t>https://jobs.dayforcehcm.com/en-US/JTEKT/CANDIDATEPORTAL/jobs/20059</t>
         </is>
       </c>
       <c r="E281" s="4" t="inlineStr">
@@ -8971,17 +8971,17 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Mechanical engineering lead</t>
+          <t>Mechanical Project Engineer</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Linewise</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="D282" s="3" t="inlineStr">
         <is>
-          <t>https://linewise.io/careers/mechanical-engineering-lead/</t>
+          <t>https://jobs.dayforcehcm.com/en-US/legence/studentportal/jobs/33975</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -9001,17 +9001,17 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Senior ATE Mechanical Engineer</t>
+          <t>Mechanical engineering lead</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Lunar Energy</t>
+          <t>Linewise</t>
         </is>
       </c>
       <c r="D283" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/lunarenergy/jobs/6210976004</t>
+          <t>https://linewise.io/careers/mechanical-engineering-lead/</t>
         </is>
       </c>
       <c r="E283" s="4" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="F283" s="4" t="inlineStr">
         <is>
-          <t>Mountain View, CA</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -9031,7 +9031,7 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Senior ATE Mechanical Engineer (Contractor)</t>
+          <t>Senior ATE Mechanical Engineer</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="D284" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/lunarenergy/jobs/6207133004</t>
+          <t>https://job-boards.greenhouse.io/lunarenergy/jobs/6210976004</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Senior Hardware Reliability Engineer - Power Electronics</t>
+          <t>Senior ATE Mechanical Engineer (Contractor)</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="D285" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/lunarenergy/jobs/6231620004</t>
+          <t>https://job-boards.greenhouse.io/lunarenergy/jobs/6207133004</t>
         </is>
       </c>
       <c r="E285" s="4" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Staff ATE Mechanical Engineer</t>
+          <t>Senior Hardware Reliability Engineer - Power Electronics</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="D286" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/lunarenergy/jobs/6214999004</t>
+          <t>https://job-boards.greenhouse.io/lunarenergy/jobs/6231620004</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -9121,7 +9121,7 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Staff ATE Mechanical Engineer (Contractor)</t>
+          <t>Staff ATE Mechanical Engineer</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="D287" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/lunarenergy/jobs/6215000004</t>
+          <t>https://job-boards.greenhouse.io/lunarenergy/jobs/6214999004</t>
         </is>
       </c>
       <c r="E287" s="4" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Staff Hardware Reliability Engineer - Power Electronics</t>
+          <t>Staff ATE Mechanical Engineer (Contractor)</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="D288" s="3" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/lunarenergy/jobs/6231621004</t>
+          <t>https://job-boards.greenhouse.io/lunarenergy/jobs/6215000004</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -9181,17 +9181,17 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">BIM Design Engineer </t>
+          <t>Staff Hardware Reliability Engineer - Power Electronics</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>Mariana Minerals</t>
+          <t>Lunar Energy</t>
         </is>
       </c>
       <c r="D289" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/marianaminerals/2839ee03-a819-4e1d-929c-3cedc9ac57c2</t>
+          <t>https://job-boards.greenhouse.io/lunarenergy/jobs/6231621004</t>
         </is>
       </c>
       <c r="E289" s="4" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>Mountain View, CA</t>
         </is>
       </c>
     </row>
@@ -9211,7 +9211,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Process Engineer</t>
+          <t xml:space="preserve">BIM Design Engineer </t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="D290" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/marianaminerals/a61ece5b-1e04-420e-8504-ae594149be52</t>
+          <t>https://jobs.ashbyhq.com/marianaminerals/2839ee03-a819-4e1d-929c-3cedc9ac57c2</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -9231,7 +9231,7 @@
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>Joaquin, TX</t>
+          <t>Houston, TX</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9251,7 @@
       </c>
       <c r="D291" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/marianaminerals/774bafd4-62ee-4fd8-a3f0-2e43019788ec</t>
+          <t>https://jobs.ashbyhq.com/marianaminerals/a61ece5b-1e04-420e-8504-ae594149be52</t>
         </is>
       </c>
       <c r="E291" s="4" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>Moab, UT</t>
+          <t>Joaquin, TX</t>
         </is>
       </c>
     </row>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Project Engineer</t>
+          <t>Process Engineer</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="D292" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/marianaminerals/869b7615-7e92-4514-a4c0-462bed10f37d</t>
+          <t>https://jobs.ashbyhq.com/marianaminerals/774bafd4-62ee-4fd8-a3f0-2e43019788ec</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sr./Staff Process Engineer - Detailed Engineering and Plant Design </t>
+          <t>Project Engineer</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="D293" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/marianaminerals/b03fb27c-9697-4ec3-9821-4785379cd172</t>
+          <t>https://jobs.ashbyhq.com/marianaminerals/869b7615-7e92-4514-a4c0-462bed10f37d</t>
         </is>
       </c>
       <c r="E293" s="4" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>Houston, TX</t>
+          <t>Moab, UT</t>
         </is>
       </c>
     </row>
@@ -9331,7 +9331,7 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Staff Mechanical Engineer</t>
+          <t xml:space="preserve">Sr./Staff Process Engineer - Detailed Engineering and Plant Design </t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="D294" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/marianaminerals/c59fd9e0-27b9-4125-bcfc-40569938359e</t>
+          <t>https://jobs.ashbyhq.com/marianaminerals/b03fb27c-9697-4ec3-9821-4785379cd172</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -9361,17 +9361,17 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Design Engineer</t>
+          <t>Staff Mechanical Engineer</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Matic Robots</t>
+          <t>Mariana Minerals</t>
         </is>
       </c>
       <c r="D295" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/Maticrobots/bfb0df27-bb17-46a1-919c-afd8c3d09a7d</t>
+          <t>https://jobs.ashbyhq.com/marianaminerals/c59fd9e0-27b9-4125-bcfc-40569938359e</t>
         </is>
       </c>
       <c r="E295" s="4" t="inlineStr">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>Menlo Park, CA</t>
+          <t>Houston, TX</t>
         </is>
       </c>
     </row>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Reliability Design Engineer - Motors, Mechanisms and Electronics</t>
+          <t>Mechanical Design Engineer</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="D296" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/Maticrobots/1858e85e-c3be-4d05-9a43-083a84ba3255</t>
+          <t>https://jobs.ashbyhq.com/Maticrobots/bfb0df27-bb17-46a1-919c-afd8c3d09a7d</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>Robotics Reliability Engineer - Motors, Mechanisms and Electronics</t>
+          <t>Reliability Design Engineer - Motors, Mechanisms and Electronics</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
@@ -9431,7 +9431,7 @@
       </c>
       <c r="D297" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/Maticrobots/76c07009-73b5-43e3-affb-d4fc20b9fe49</t>
+          <t>https://jobs.ashbyhq.com/Maticrobots/1858e85e-c3be-4d05-9a43-083a84ba3255</t>
         </is>
       </c>
       <c r="E297" s="4" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Senior Manufacturing Design Engineer</t>
+          <t>Robotics Reliability Engineer - Motors, Mechanisms and Electronics</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="D298" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/Maticrobots/c1e04901-0c2c-4902-b4fc-af5fa9515748</t>
+          <t>https://jobs.ashbyhq.com/Maticrobots/76c07009-73b5-43e3-affb-d4fc20b9fe49</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -9481,7 +9481,7 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Senior Mechanical Design Engineer</t>
+          <t>Senior Manufacturing Design Engineer</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="D299" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/Maticrobots/f46b52d3-0d7f-4b28-979e-26a99d380c73</t>
+          <t>https://jobs.ashbyhq.com/Maticrobots/c1e04901-0c2c-4902-b4fc-af5fa9515748</t>
         </is>
       </c>
       <c r="E299" s="4" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Systems Engineer (Firmware)</t>
+          <t>Senior Mechanical Design Engineer</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="D300" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/Maticrobots/b6623c4c-afd2-4f7e-b364-6ed7f6b0bbd3</t>
+          <t>https://jobs.ashbyhq.com/Maticrobots/f46b52d3-0d7f-4b28-979e-26a99d380c73</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>Systems Engineer (Rust)</t>
+          <t>Systems Engineer (Firmware)</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="D301" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/Maticrobots/56979df7-cb5e-45c3-baa9-3e1d9c8c2eb0</t>
+          <t>https://jobs.ashbyhq.com/Maticrobots/b6623c4c-afd2-4f7e-b364-6ed7f6b0bbd3</t>
         </is>
       </c>
       <c r="E301" s="4" t="inlineStr">
@@ -9571,17 +9571,17 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Business Process Engineer II</t>
+          <t>Systems Engineer (Rust)</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Panasonic</t>
+          <t>Matic Robots</t>
         </is>
       </c>
       <c r="D302" s="3" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/50918?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://jobs.ashbyhq.com/Maticrobots/56979df7-cb5e-45c3-baa9-3e1d9c8c2eb0</t>
         </is>
       </c>
       <c r="E302" s="2" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>Location Sparks, Nevada US</t>
+          <t>Menlo Park, CA</t>
         </is>
       </c>
     </row>
@@ -9601,7 +9601,7 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Design Engineer</t>
+          <t>Business Process Engineer II</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="D303" s="5" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/51952?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/50918?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E303" s="4" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="D304" s="3" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/51081?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/51952?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E304" s="2" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Hardware Engineer I</t>
+          <t>Design Engineer</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="D305" s="5" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/50889?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/51081?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E305" s="4" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Manager, Materials Engineering</t>
+          <t>Hardware Engineer I</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="D306" s="3" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/50602?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/50889?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E306" s="2" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineer I</t>
+          <t>Manager, Materials Engineering</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="D307" s="5" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/50468?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/50602?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E307" s="4" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="D308" s="3" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/50560?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/50468?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E308" s="2" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineer II</t>
+          <t>Manufacturing Engineer I</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="D309" s="5" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/50152?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/50560?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E309" s="4" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="D310" s="3" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/48385?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/50152?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E310" s="2" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Engineer III</t>
+          <t>Manufacturing Engineer II</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="D311" s="5" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/51890?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/48385?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E311" s="4" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="D312" s="3" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/51590?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/51890?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E312" s="2" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="D313" s="5" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/51098?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/51590?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E313" s="4" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="D314" s="3" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/50459?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/51098?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E314" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>Materials Engineer III</t>
+          <t>Manufacturing Engineer III</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="D315" s="5" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/51846?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/50459?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E315" s="4" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineer II</t>
+          <t>Materials Engineer III</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="D316" s="3" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/50556?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/51846?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E316" s="2" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>Process Engineer I</t>
+          <t>Mechanical Engineer II</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="D317" s="5" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/51951?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/50556?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E317" s="4" t="inlineStr">
@@ -10061,7 +10061,7 @@
       </c>
       <c r="D318" s="3" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/51889?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/51951?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E318" s="2" t="inlineStr">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>Process Engineer II - Formation, Inspection Team</t>
+          <t>Process Engineer I</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="D319" s="5" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/51204?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/51889?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E319" s="4" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Process Engineer III, Electrode</t>
+          <t>Process Engineer II - Formation, Inspection Team</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="D320" s="3" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/49103?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/51204?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E320" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>Project Engineer III</t>
+          <t>Process Engineer III, Electrode</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="D321" s="5" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/49875?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/49103?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E321" s="4" t="inlineStr">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>Structural Stress Engineer IV- FEA (Nastran/Patran)</t>
+          <t>Project Engineer III</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="D322" s="3" t="inlineStr">
         <is>
-          <t>https://careers.na.panasonic.com/jobs/51316?lang=en-us&amp;previousLocale=en-US</t>
+          <t>https://careers.na.panasonic.com/jobs/49875?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E322" s="2" t="inlineStr">
@@ -10201,17 +10201,17 @@
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>Associate Process Engineer</t>
+          <t>Structural Stress Engineer IV- FEA (Nastran/Patran)</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Quantum Computing Inc</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="D323" s="5" t="inlineStr">
         <is>
-          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1069479/associate-process-engineer</t>
+          <t>https://careers.na.panasonic.com/jobs/51316?lang=en-us&amp;previousLocale=en-US</t>
         </is>
       </c>
       <c r="E323" s="4" t="inlineStr">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Location Sparks, Nevada US</t>
         </is>
       </c>
     </row>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>Equipment Engineer</t>
+          <t>Associate Process Engineer</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="D324" s="3" t="inlineStr">
         <is>
-          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1055828/equipment-engineer</t>
+          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1069479/associate-process-engineer</t>
         </is>
       </c>
       <c r="E324" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>FPGA Design Engineer</t>
+          <t>Equipment Engineer</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="D325" s="5" t="inlineStr">
         <is>
-          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1059889/fpga-design-engineer</t>
+          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1055828/equipment-engineer</t>
         </is>
       </c>
       <c r="E325" s="4" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Engineer-Photonics</t>
+          <t>FPGA Design Engineer</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="D326" s="3" t="inlineStr">
         <is>
-          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1042948/mechanical-engineer-photonics</t>
+          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1059889/fpga-design-engineer</t>
         </is>
       </c>
       <c r="E326" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>Process Engineer</t>
+          <t>Mechanical Engineer-Photonics</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="D327" s="5" t="inlineStr">
         <is>
-          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1056926/process-engineer</t>
+          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1042948/mechanical-engineer-photonics</t>
         </is>
       </c>
       <c r="E327" s="4" t="inlineStr">
@@ -10351,7 +10351,7 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>Process Engineer Technician</t>
+          <t>Process Engineer</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="D328" s="3" t="inlineStr">
         <is>
-          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1056928/process-engineer-technician</t>
+          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1056926/process-engineer</t>
         </is>
       </c>
       <c r="E328" s="2" t="inlineStr">
@@ -10381,7 +10381,7 @@
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>Reliability Test Engineer</t>
+          <t>Process Engineer Technician</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="D329" s="5" t="inlineStr">
         <is>
-          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1048000/reliability-test-engineer</t>
+          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1056928/process-engineer-technician</t>
         </is>
       </c>
       <c r="E329" s="4" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>Semiconductor Process Engineer</t>
+          <t>Reliability Test Engineer</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="D330" s="3" t="inlineStr">
         <is>
-          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1023287/semiconductor-process-engineer</t>
+          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1048000/reliability-test-engineer</t>
         </is>
       </c>
       <c r="E330" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>Senior Automation Engineer-Industrial</t>
+          <t>Semiconductor Process Engineer</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="D331" s="5" t="inlineStr">
         <is>
-          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1019727/senior-automation-engineer-industrial</t>
+          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1023287/semiconductor-process-engineer</t>
         </is>
       </c>
       <c r="E331" s="4" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>Senior Manufacturing Engineer</t>
+          <t>Senior Automation Engineer-Industrial</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="D332" s="3" t="inlineStr">
         <is>
-          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1064606/senior-manufacturing-engineer</t>
+          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1019727/senior-automation-engineer-industrial</t>
         </is>
       </c>
       <c r="E332" s="2" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>Senior Process Engineer</t>
+          <t>Senior Manufacturing Engineer</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
@@ -10511,7 +10511,7 @@
       </c>
       <c r="D333" s="5" t="inlineStr">
         <is>
-          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1060400/senior-process-engineer</t>
+          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1064606/senior-manufacturing-engineer</t>
         </is>
       </c>
       <c r="E333" s="4" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>Senior Process Engineer - H1</t>
+          <t>Senior Process Engineer</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="D334" s="3" t="inlineStr">
         <is>
-          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1020291/senior-process-engineer-h1</t>
+          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1060400/senior-process-engineer</t>
         </is>
       </c>
       <c r="E334" s="2" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>Senior Quality Engineer</t>
+          <t>Senior Process Engineer - H1</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="D335" s="5" t="inlineStr">
         <is>
-          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1025949/senior-quality-engineer</t>
+          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1020291/senior-process-engineer-h1</t>
         </is>
       </c>
       <c r="E335" s="4" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>Test Engineer, Hardware</t>
+          <t>Senior Quality Engineer</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="D336" s="3" t="inlineStr">
         <is>
-          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1020367/test-engineer-hardware</t>
+          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1025949/senior-quality-engineer</t>
         </is>
       </c>
       <c r="E336" s="2" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>Test Engineer-Photonics</t>
+          <t>Test Engineer, Hardware</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="D337" s="5" t="inlineStr">
         <is>
-          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1042961/test-engineer-photonics</t>
+          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1020367/test-engineer-hardware</t>
         </is>
       </c>
       <c r="E337" s="4" t="inlineStr">
@@ -10651,17 +10651,17 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>Associate Product Design Engineer</t>
+          <t>Test Engineer-Photonics</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Schaeffler</t>
+          <t>Quantum Computing Inc</t>
         </is>
       </c>
       <c r="D338" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Wooster%2C-OH-Associate-Product-Design-Engineer-OH-44691/1442072033/</t>
+          <t>https://quantum-computing-inc.alphastaff-hiring.com/job/1042961/test-engineer-photonics</t>
         </is>
       </c>
       <c r="E338" s="2" t="inlineStr">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="B339" s="4" t="inlineStr">
         <is>
-          <t>Ausbildung Elektroniker/in für Betriebstechnik 2027 (d/m/w)</t>
+          <t>Associate Product Design Engineer</t>
         </is>
       </c>
       <c r="C339" s="4" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="D339" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Lahr-Ausbildung-Elektronikerin-f%C3%BCr-Betriebstechnik-2027-%28dmw%29-77933/1415698433/</t>
+          <t>https://jobs.schaeffler.com/job/Wooster%2C-OH-Associate-Product-Design-Engineer-OH-44691/1442072033/</t>
         </is>
       </c>
       <c r="E339" s="4" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>Ausbildung Industriemechaniker (d/m/w) 2027</t>
+          <t>Ausbildung Elektroniker/in für Betriebstechnik 2027 (d/m/w)</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="D340" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Gunzenhausen-Ausbildung-Industriemechaniker-%28dmw%29-2027-91710/1409877733/</t>
+          <t>https://jobs.schaeffler.com/job/Lahr-Ausbildung-Elektronikerin-f%C3%BCr-Betriebstechnik-2027-%28dmw%29-77933/1415698433/</t>
         </is>
       </c>
       <c r="E340" s="2" t="inlineStr">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="D341" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/H%C3%B6chstadt-Ausbildung-Industriemechaniker-%28dmw%29-2027-91315/1409285633/</t>
+          <t>https://jobs.schaeffler.com/job/Gunzenhausen-Ausbildung-Industriemechaniker-%28dmw%29-2027-91710/1409877733/</t>
         </is>
       </c>
       <c r="E341" s="4" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="D342" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Hirschaid-Ausbildung-Industriemechaniker-%28dmw%29-2027-96114/1408847733/</t>
+          <t>https://jobs.schaeffler.com/job/H%C3%B6chstadt-Ausbildung-Industriemechaniker-%28dmw%29-2027-91315/1409285633/</t>
         </is>
       </c>
       <c r="E342" s="2" t="inlineStr">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="D343" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Schweinfurt-Ausbildung-Industriemechaniker-%28dmw%29-2027-97421/1430349733/</t>
+          <t>https://jobs.schaeffler.com/job/Hirschaid-Ausbildung-Industriemechaniker-%28dmw%29-2027-96114/1408847733/</t>
         </is>
       </c>
       <c r="E343" s="4" t="inlineStr">
@@ -10841,7 +10841,7 @@
       </c>
       <c r="D344" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Homburg-Ausbildung-Industriemechaniker-%28dmw%29-2027-66424/1429640333/</t>
+          <t>https://jobs.schaeffler.com/job/Schweinfurt-Ausbildung-Industriemechaniker-%28dmw%29-2027-97421/1430349733/</t>
         </is>
       </c>
       <c r="E344" s="2" t="inlineStr">
@@ -10861,7 +10861,7 @@
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>Ausbildung Industriemechaniker (d/m/w) Suhl 2027</t>
+          <t>Ausbildung Industriemechaniker (d/m/w) 2027</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr">
@@ -10871,7 +10871,7 @@
       </c>
       <c r="D345" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Suhl-Ausbildung-Industriemechaniker-%28dmw%29-Suhl-2027-98527/1430997933/</t>
+          <t>https://jobs.schaeffler.com/job/Homburg-Ausbildung-Industriemechaniker-%28dmw%29-2027-66424/1429640333/</t>
         </is>
       </c>
       <c r="E345" s="4" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>Ausbildung Industriemechaniker/in (d/m/w) 2027</t>
+          <t>Ausbildung Industriemechaniker (d/m/w) Suhl 2027</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
@@ -10901,7 +10901,7 @@
       </c>
       <c r="D346" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Lahr-Ausbildung-Industriemechanikerin-%28dmw%29-2027-77933/1415706133/</t>
+          <t>https://jobs.schaeffler.com/job/Suhl-Ausbildung-Industriemechaniker-%28dmw%29-Suhl-2027-98527/1430997933/</t>
         </is>
       </c>
       <c r="E346" s="2" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
-          <t>Ausbildung Maschinen- und Anlagenführer (d/m/w) 2027</t>
+          <t>Ausbildung Industriemechaniker/in (d/m/w) 2027</t>
         </is>
       </c>
       <c r="C347" s="4" t="inlineStr">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="D347" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Hirschaid-Ausbildung-Maschinen-und-Anlagenf%C3%BChrer-%28dmw%29-2027-96114/1408786033/</t>
+          <t>https://jobs.schaeffler.com/job/Lahr-Ausbildung-Industriemechanikerin-%28dmw%29-2027-77933/1415706133/</t>
         </is>
       </c>
       <c r="E347" s="4" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>Ausbildung Mechatroniker (d/m/w) 2027</t>
+          <t>Ausbildung Maschinen- und Anlagenführer (d/m/w) 2027</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="D348" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Hirschaid-Ausbildung-Mechatroniker-%28dmw%29-2027-96114/1408836833/</t>
+          <t>https://jobs.schaeffler.com/job/Hirschaid-Ausbildung-Maschinen-und-Anlagenf%C3%BChrer-%28dmw%29-2027-96114/1408786033/</t>
         </is>
       </c>
       <c r="E348" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="D349" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/H%C3%B6chstadt-Ausbildung-Mechatroniker-%28dmw%29-2027-91315/1408868733/</t>
+          <t>https://jobs.schaeffler.com/job/Hirschaid-Ausbildung-Mechatroniker-%28dmw%29-2027-96114/1408836833/</t>
         </is>
       </c>
       <c r="E349" s="4" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="D350" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Herzogenaurach-Ausbildung-Mechatroniker-%28dmw%29-2027-91074/1410336733/</t>
+          <t>https://jobs.schaeffler.com/job/H%C3%B6chstadt-Ausbildung-Mechatroniker-%28dmw%29-2027-91315/1408868733/</t>
         </is>
       </c>
       <c r="E350" s="2" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="D351" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Schweinfurt-Ausbildung-Mechatroniker-%28dmw%29-2027-97421/1430354833/</t>
+          <t>https://jobs.schaeffler.com/job/Herzogenaurach-Ausbildung-Mechatroniker-%28dmw%29-2027-91074/1410336733/</t>
         </is>
       </c>
       <c r="E351" s="4" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="D352" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Homburg-Ausbildung-Mechatroniker-%28dmw%29-2027-66424/1429637733/</t>
+          <t>https://jobs.schaeffler.com/job/Schweinfurt-Ausbildung-Mechatroniker-%28dmw%29-2027-97421/1430354833/</t>
         </is>
       </c>
       <c r="E352" s="2" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="B353" s="4" t="inlineStr">
         <is>
-          <t>Ausbildung Werkzeugmechaniker (d/m/w) 2027</t>
+          <t>Ausbildung Mechatroniker (d/m/w) 2027</t>
         </is>
       </c>
       <c r="C353" s="4" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="D353" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/H%C3%B6chstadt-Ausbildung-Werkzeugmechaniker-%28dmw%29-2027-91315/1409237233/</t>
+          <t>https://jobs.schaeffler.com/job/Homburg-Ausbildung-Mechatroniker-%28dmw%29-2027-66424/1429637733/</t>
         </is>
       </c>
       <c r="E353" s="4" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="D354" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Hirschaid-Ausbildung-Werkzeugmechaniker-%28dmw%29-2027-96114/1408734033/</t>
+          <t>https://jobs.schaeffler.com/job/H%C3%B6chstadt-Ausbildung-Werkzeugmechaniker-%28dmw%29-2027-91315/1409237233/</t>
         </is>
       </c>
       <c r="E354" s="2" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="B355" s="4" t="inlineStr">
         <is>
-          <t>Duales Studium (DHBW) - Cyber Security (d/m/w) 2027</t>
+          <t>Ausbildung Werkzeugmechaniker (d/m/w) 2027</t>
         </is>
       </c>
       <c r="C355" s="4" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="D355" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Herzogenaurach-Duales-Studium-%28DHBW%29-Cyber-Security-%28dmw%29-2027-91074/1410443233/</t>
+          <t>https://jobs.schaeffler.com/job/Hirschaid-Ausbildung-Werkzeugmechaniker-%28dmw%29-2027-96114/1408734033/</t>
         </is>
       </c>
       <c r="E355" s="4" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>Duales Studium (DHBW) - Elektrotechnik und Informationstechnik (d/m/w) 2027</t>
+          <t>Duales Studium (DHBW) - Cyber Security (d/m/w) 2027</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="D356" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Herzogenaurach-Duales-Studium-%28DHBW%29-Elektrotechnik-und-Informationstechnik-%28dmw%29-2027-91074/1410428233/</t>
+          <t>https://jobs.schaeffler.com/job/Herzogenaurach-Duales-Studium-%28DHBW%29-Cyber-Security-%28dmw%29-2027-91074/1410443233/</t>
         </is>
       </c>
       <c r="E356" s="2" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="B357" s="4" t="inlineStr">
         <is>
-          <t>Duales Studium (DHBW) - Informatik (d/m/w) 2027</t>
+          <t>Duales Studium (DHBW) - Elektrotechnik und Informationstechnik (d/m/w) 2027</t>
         </is>
       </c>
       <c r="C357" s="4" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="D357" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Hirschaid-Duales-Studium-%28DHBW%29-Informatik-%28dmw%29-2027-96114/1410207133/</t>
+          <t>https://jobs.schaeffler.com/job/Herzogenaurach-Duales-Studium-%28DHBW%29-Elektrotechnik-und-Informationstechnik-%28dmw%29-2027-91074/1410428233/</t>
         </is>
       </c>
       <c r="E357" s="4" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>Duales Studium (DHBW) - Integrated Engineering (d/m/w) 2027</t>
+          <t>Duales Studium (DHBW) - Informatik (d/m/w) 2027</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Herzogenaurach-Duales-Studium-%28DHBW%29-Integrated-Engineering-%28dmw%29-2027-91074/1410436233/</t>
+          <t>https://jobs.schaeffler.com/job/Hirschaid-Duales-Studium-%28DHBW%29-Informatik-%28dmw%29-2027-96114/1410207133/</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="B359" s="4" t="inlineStr">
         <is>
-          <t>Duales Studium (DHBW) - Wirtschaftsingenieurwesen digitale Transformation (d/m/w) 2027</t>
+          <t>Duales Studium (DHBW) - Integrated Engineering (d/m/w) 2027</t>
         </is>
       </c>
       <c r="C359" s="4" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="D359" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Homburg-Duales-Studium-%28DHBW%29-Wirtschaftsingenieurwesen-digitale-Transformation-%28dmw%29-2027-66424/1429942933/</t>
+          <t>https://jobs.schaeffler.com/job/Herzogenaurach-Duales-Studium-%28DHBW%29-Integrated-Engineering-%28dmw%29-2027-91074/1410436233/</t>
         </is>
       </c>
       <c r="E359" s="4" t="inlineStr">
@@ -11311,7 +11311,7 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>Electric Hardware Engineer</t>
+          <t>Duales Studium (DHBW) - Wirtschaftsingenieurwesen digitale Transformation (d/m/w) 2027</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Yokohama-Electric-Hardware-Engineer-221-0031/1408154333/</t>
+          <t>https://jobs.schaeffler.com/job/Homburg-Duales-Studium-%28DHBW%29-Wirtschaftsingenieurwesen-digitale-Transformation-%28dmw%29-2027-66424/1429942933/</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="B361" s="4" t="inlineStr">
         <is>
-          <t>Engineer - Manufacturing Quality Engineering</t>
+          <t>Electric Hardware Engineer</t>
         </is>
       </c>
       <c r="C361" s="4" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="D361" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Fort-Mill%2C-SC-Engineer-Manufacturing-Quality-Engineering-SC-29715/1448141433/</t>
+          <t>https://jobs.schaeffler.com/job/Yokohama-Electric-Hardware-Engineer-221-0031/1408154333/</t>
         </is>
       </c>
       <c r="E361" s="4" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>Facility Maintenance Engineer</t>
+          <t>Engineer - Manufacturing Quality Engineering</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="D362" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Fort-Mill%2C-SC-Facility-Maintenance-Engineer-SC-29715/1419425833/</t>
+          <t>https://jobs.schaeffler.com/job/Fort-Mill%2C-SC-Engineer-Manufacturing-Quality-Engineering-SC-29715/1448141433/</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="B363" s="4" t="inlineStr">
         <is>
-          <t>Group Leader, Manufacturing Quality Engineering</t>
+          <t>Facility Maintenance Engineer</t>
         </is>
       </c>
       <c r="C363" s="4" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="D363" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Wooster%2C-OH-Group-Leader%2C-Manufacturing-Quality-Engineering-OH-44691/1431268733/</t>
+          <t>https://jobs.schaeffler.com/job/Fort-Mill%2C-SC-Facility-Maintenance-Engineer-SC-29715/1419425833/</t>
         </is>
       </c>
       <c r="E363" s="4" t="inlineStr">
@@ -11431,7 +11431,7 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>Industrial Mechanical Maintenance Apprentice</t>
+          <t>Group Leader, Manufacturing Quality Engineering</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="D364" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Danbury%2C-CT-Industrial-Mechanical-Maintenance-Apprentice-CT-6813/1389462933/</t>
+          <t>https://jobs.schaeffler.com/job/Wooster%2C-OH-Group-Leader%2C-Manufacturing-Quality-Engineering-OH-44691/1431268733/</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -11461,7 +11461,7 @@
       </c>
       <c r="B365" s="4" t="inlineStr">
         <is>
-          <t>Industrial Mechatronics Mechanic Apprentice - Winsted</t>
+          <t>Industrial Mechanical Maintenance Apprentice</t>
         </is>
       </c>
       <c r="C365" s="4" t="inlineStr">
@@ -11471,7 +11471,7 @@
       </c>
       <c r="D365" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Winsted%2C-CT-Industrial-Mechatronics-Mechanic-Apprentice-Winsted-CT-6098/1414386933/</t>
+          <t>https://jobs.schaeffler.com/job/Danbury%2C-CT-Industrial-Mechanical-Maintenance-Apprentice-CT-6813/1389462933/</t>
         </is>
       </c>
       <c r="E365" s="4" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing Engineer (Stamping)</t>
+          <t>Industrial Mechatronics Mechanic Apprentice - Winsted</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="D366" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Fort-Mill%2C-SC-Manufacturing-Engineer-%28Stamping%29-SC-29715/1428456733/</t>
+          <t>https://jobs.schaeffler.com/job/Winsted%2C-CT-Industrial-Mechatronics-Mechanic-Apprentice-Winsted-CT-6098/1414386933/</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="B367" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing Technology Engineer (Mechatronics and Humanoid Assembly)</t>
+          <t>Manufacturing Engineer (Stamping)</t>
         </is>
       </c>
       <c r="C367" s="4" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="D367" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Fort-Mill%2C-SC-Manufacturing-Technology-Engineer-%28Mechatronics-and-Humanoid-Assembly%29-SC-29715/1428455733/</t>
+          <t>https://jobs.schaeffler.com/job/Fort-Mill%2C-SC-Manufacturing-Engineer-%28Stamping%29-SC-29715/1428456733/</t>
         </is>
       </c>
       <c r="E367" s="4" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Application Engineer</t>
+          <t>Manufacturing Technology Engineer (Mechatronics and Humanoid Assembly)</t>
         </is>
       </c>
       <c r="C368" s="2" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="D368" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Brasov-Mechanical-Application-Engineer-507075/1434840633/</t>
+          <t>https://jobs.schaeffler.com/job/Fort-Mill%2C-SC-Manufacturing-Technology-Engineer-%28Mechatronics-and-Humanoid-Assembly%29-SC-29715/1428455733/</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="B369" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Design Engineer (Aerospace)</t>
+          <t>Mechanical Application Engineer</t>
         </is>
       </c>
       <c r="C369" s="4" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="D369" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Danbury%2C-CT-Mechanical-Design-Engineer-%28Aerospace%29-CT-6813/1450427133/</t>
+          <t>https://jobs.schaeffler.com/job/Brasov-Mechanical-Application-Engineer-507075/1434840633/</t>
         </is>
       </c>
       <c r="E369" s="4" t="inlineStr">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Eng.</t>
+          <t>Mechanical Design Engineer (Aerospace)</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="D370" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Brasov-Mechanical-Eng_-507075/1434270333/</t>
+          <t>https://jobs.schaeffler.com/job/Danbury%2C-CT-Mechanical-Design-Engineer-%28Aerospace%29-CT-6813/1450427133/</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="B371" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Technician - 1st Shift</t>
+          <t>Mechanical Eng.</t>
         </is>
       </c>
       <c r="C371" s="4" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="D371" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Fort-Mill%2C-SC-Mechanical-Maintenance-Technician-1st-Shift-SC-29715/1412501233/</t>
+          <t>https://jobs.schaeffler.com/job/Brasov-Mechanical-Eng_-507075/1434270333/</t>
         </is>
       </c>
       <c r="E371" s="4" t="inlineStr">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Maintenance Technician - 3rd Shift</t>
+          <t>Mechanical Maintenance Technician - 1st Shift</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="D372" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Fort-Mill%2C-SC-Mechanical-Maintenance-Technician-3rd-Shift-SC-29715/1418843133/</t>
+          <t>https://jobs.schaeffler.com/job/Fort-Mill%2C-SC-Mechanical-Maintenance-Technician-1st-Shift-SC-29715/1412501233/</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -11701,7 +11701,7 @@
       </c>
       <c r="B373" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Product Design Engineer</t>
+          <t>Mechanical Maintenance Technician - 3rd Shift</t>
         </is>
       </c>
       <c r="C373" s="4" t="inlineStr">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="D373" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Chonburi-Mechanical-Product-Design-Engineer-20110/1452021933/</t>
+          <t>https://jobs.schaeffler.com/job/Fort-Mill%2C-SC-Mechanical-Maintenance-Technician-3rd-Shift-SC-29715/1418843133/</t>
         </is>
       </c>
       <c r="E373" s="4" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Techn.</t>
+          <t>Mechanical Product Design Engineer</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="D374" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Brasov-Mechanical-Techn_-507075/1434337133/</t>
+          <t>https://jobs.schaeffler.com/job/Chonburi-Mechanical-Product-Design-Engineer-20110/1452021933/</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="B375" s="4" t="inlineStr">
         <is>
-          <t>Product Design Engineer - Battery Systems</t>
+          <t>Mechanical Techn.</t>
         </is>
       </c>
       <c r="C375" s="4" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="D375" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Wooster%2C-OH-Product-Design-Engineer-Battery-Systems-OH-44691/1271308701/</t>
+          <t>https://jobs.schaeffler.com/job/Brasov-Mechanical-Techn_-507075/1434337133/</t>
         </is>
       </c>
       <c r="E375" s="4" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="B376" s="2" t="inlineStr">
         <is>
-          <t>Quality Engineer, BD ETS, Division PTC JSEAP</t>
+          <t>Product Design Engineer - Battery Systems</t>
         </is>
       </c>
       <c r="C376" s="2" t="inlineStr">
@@ -11801,7 +11801,7 @@
       </c>
       <c r="D376" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Yokohama-Quality-Engineer%2C-BD-ETS%2C-Division-PTC-JSEAP-221-0031/1366170833/</t>
+          <t>https://jobs.schaeffler.com/job/Wooster%2C-OH-Product-Design-Engineer-Battery-Systems-OH-44691/1271308701/</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="B377" s="4" t="inlineStr">
         <is>
-          <t>Senior Tooling Engineer</t>
+          <t>Quality Engineer, BD ETS, Division PTC JSEAP</t>
         </is>
       </c>
       <c r="C377" s="4" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="D377" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Danbury%2C-CT-Senior-Tooling-Engineer-CT-6813/1450418633/</t>
+          <t>https://jobs.schaeffler.com/job/Yokohama-Quality-Engineer%2C-BD-ETS%2C-Division-PTC-JSEAP-221-0031/1366170833/</t>
         </is>
       </c>
       <c r="E377" s="4" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t>Sr. Mechanical Design Engineer (Gearing - Humanoid Robotics)</t>
+          <t>Senior Tooling Engineer</t>
         </is>
       </c>
       <c r="C378" s="2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="D378" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Troy%2C-MI-Sr_-Mechanical-Design-Engineer-%28Gearing-Humanoid-Robotics%29-MI-48083/1435395233/</t>
+          <t>https://jobs.schaeffler.com/job/Danbury%2C-CT-Senior-Tooling-Engineer-CT-6813/1450418633/</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="B379" s="4" t="inlineStr">
         <is>
-          <t>Sr. Systems Engineer (Sensors - Humanoid Robotics)</t>
+          <t>Sr. Mechanical Design Engineer (Gearing - Humanoid Robotics)</t>
         </is>
       </c>
       <c r="C379" s="4" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="D379" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Troy%2C-MI-Sr_-Systems-Engineer-%28Sensors-Humanoid-Robotics%29-MI-48083/1426681433/</t>
+          <t>https://jobs.schaeffler.com/job/Troy%2C-MI-Sr_-Mechanical-Design-Engineer-%28Gearing-Humanoid-Robotics%29-MI-48083/1435395233/</t>
         </is>
       </c>
       <c r="E379" s="4" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="B380" s="2" t="inlineStr">
         <is>
-          <t>Supplier Quality Engineer - Battery Plant</t>
+          <t>Sr. Systems Engineer (Sensors - Humanoid Robotics)</t>
         </is>
       </c>
       <c r="C380" s="2" t="inlineStr">
@@ -11921,7 +11921,7 @@
       </c>
       <c r="D380" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Wooster%2C-OH-Supplier-Quality-Engineer-Battery-Plant-OH-44691/1415519733/</t>
+          <t>https://jobs.schaeffler.com/job/Troy%2C-MI-Sr_-Systems-Engineer-%28Sensors-Humanoid-Robotics%29-MI-48083/1426681433/</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="B381" s="4" t="inlineStr">
         <is>
-          <t>Supplier Quality Engineer - Wooster Plant</t>
+          <t>Supplier Quality Engineer - Battery Plant</t>
         </is>
       </c>
       <c r="C381" s="4" t="inlineStr">
@@ -11951,7 +11951,7 @@
       </c>
       <c r="D381" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Wooster%2C-OH-Supplier-Quality-Engineer-Wooster-Plant-OH-44691/1417946133/</t>
+          <t>https://jobs.schaeffler.com/job/Wooster%2C-OH-Supplier-Quality-Engineer-Battery-Plant-OH-44691/1415519733/</t>
         </is>
       </c>
       <c r="E381" s="4" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>Supplier Quality Engineer - Wooster Plant</t>
         </is>
       </c>
       <c r="C382" s="2" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="D382" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Sofia-Test-Engineer-1504/1427701233/</t>
+          <t>https://jobs.schaeffler.com/job/Wooster%2C-OH-Supplier-Quality-Engineer-Wooster-Plant-OH-44691/1417946133/</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="B383" s="4" t="inlineStr">
         <is>
-          <t>机械工程师 Mechanical Eng.（南京）</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="C383" s="4" t="inlineStr">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="D383" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Nanjing-%E6%9C%BA%E6%A2%B0%E5%B7%A5%E7%A8%8B%E5%B8%88-Mechanical-Eng_%EF%BC%88%E5%8D%97%E4%BA%AC%EF%BC%89-211100/1434386633/</t>
+          <t>https://jobs.schaeffler.com/job/Sofia-Test-Engineer-1504/1427701233/</t>
         </is>
       </c>
       <c r="E383" s="4" t="inlineStr">
@@ -12031,7 +12031,7 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t>机械设计Mechanical Eng.(南京)</t>
+          <t>机械工程师 Mechanical Eng.（南京）</t>
         </is>
       </c>
       <c r="C384" s="2" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="D384" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Nanjing-%E6%9C%BA%E6%A2%B0%E8%AE%BE%E8%AE%A1Mechanical-Eng_%28%E5%8D%97%E4%BA%AC%29-211100/1439850433/</t>
+          <t>https://jobs.schaeffler.com/job/Nanjing-%E6%9C%BA%E6%A2%B0%E5%B7%A5%E7%A8%8B%E5%B8%88-Mechanical-Eng_%EF%BC%88%E5%8D%97%E4%BA%AC%EF%BC%89-211100/1434386633/</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="B385" s="4" t="inlineStr">
         <is>
-          <t>资深非标测试台架开发机械设计工程师 Mechanical Eng.（上海）</t>
+          <t>机械设计Mechanical Eng.(南京)</t>
         </is>
       </c>
       <c r="C385" s="4" t="inlineStr">
@@ -12071,7 +12071,7 @@
       </c>
       <c r="D385" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Anting-%E8%B5%84%E6%B7%B1%E9%9D%9E%E6%A0%87%E6%B5%8B%E8%AF%95%E5%8F%B0%E6%9E%B6%E5%BC%80%E5%8F%91%E6%9C%BA%E6%A2%B0%E8%AE%BE%E8%AE%A1%E5%B7%A5%E7%A8%8B%E5%B8%88-Mechanical-Eng_%EF%BC%88%E4%B8%8A%E6%B5%B7%EF%BC%89-201805/1403274833/</t>
+          <t>https://jobs.schaeffler.com/job/Nanjing-%E6%9C%BA%E6%A2%B0%E8%AE%BE%E8%AE%A1Mechanical-Eng_%28%E5%8D%97%E4%BA%AC%29-211100/1439850433/</t>
         </is>
       </c>
       <c r="E385" s="4" t="inlineStr">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="B386" s="2" t="inlineStr">
         <is>
-          <t>高压控制器机械设计工程师Mechanical Design Eng.（上海）</t>
+          <t>资深非标测试台架开发机械设计工程师 Mechanical Eng.（上海）</t>
         </is>
       </c>
       <c r="C386" s="2" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="D386" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.schaeffler.com/job/Anting-%E9%AB%98%E5%8E%8B%E6%8E%A7%E5%88%B6%E5%99%A8%E6%9C%BA%E6%A2%B0%E8%AE%BE%E8%AE%A1%E5%B7%A5%E7%A8%8B%E5%B8%88Mechanical-Design-Eng_%EF%BC%88%E4%B8%8A%E6%B5%B7%EF%BC%89-201805/1447119833/</t>
+          <t>https://jobs.schaeffler.com/job/Anting-%E8%B5%84%E6%B7%B1%E9%9D%9E%E6%A0%87%E6%B5%8B%E8%AF%95%E5%8F%B0%E6%9E%B6%E5%BC%80%E5%8F%91%E6%9C%BA%E6%A2%B0%E8%AE%BE%E8%AE%A1%E5%B7%A5%E7%A8%8B%E5%B8%88-Mechanical-Eng_%EF%BC%88%E4%B8%8A%E6%B5%B7%EF%BC%89-201805/1403274833/</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
@@ -12121,17 +12121,17 @@
       </c>
       <c r="B387" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Engineer</t>
+          <t>高压控制器机械设计工程师Mechanical Design Eng.（上海）</t>
         </is>
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>Shinkei</t>
+          <t>Schaeffler</t>
         </is>
       </c>
       <c r="D387" s="5" t="inlineStr">
         <is>
-          <t>https://careers.kula.ai/shinkei/32624-mechanical-engineer</t>
+          <t>https://jobs.schaeffler.com/job/Anting-%E9%AB%98%E5%8E%8B%E6%8E%A7%E5%88%B6%E5%99%A8%E6%9C%BA%E6%A2%B0%E8%AE%BE%E8%AE%A1%E5%B7%A5%E7%A8%8B%E5%B8%88Mechanical-Design-Eng_%EF%BC%88%E4%B8%8A%E6%B5%B7%EF%BC%89-201805/1447119833/</t>
         </is>
       </c>
       <c r="E387" s="4" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="B388" s="2" t="inlineStr">
         <is>
-          <t>New Product Commercialization Manager</t>
+          <t>Mechanical Engineer</t>
         </is>
       </c>
       <c r="C388" s="2" t="inlineStr">
@@ -12161,7 +12161,7 @@
       </c>
       <c r="D388" s="3" t="inlineStr">
         <is>
-          <t>https://careers.kula.ai/shinkei/34690-new-product-commercialization-manager</t>
+          <t>https://careers.kula.ai/shinkei/32624-mechanical-engineer</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="B389" s="4" t="inlineStr">
         <is>
-          <t>Test Engineer</t>
+          <t>New Product Commercialization Manager</t>
         </is>
       </c>
       <c r="C389" s="4" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="D389" s="5" t="inlineStr">
         <is>
-          <t>https://careers.kula.ai/shinkei/50714-test-engineer</t>
+          <t>https://careers.kula.ai/shinkei/34690-new-product-commercialization-manager</t>
         </is>
       </c>
       <c r="E389" s="4" t="inlineStr">
@@ -12211,17 +12211,17 @@
       </c>
       <c r="B390" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing Engineer</t>
+          <t>Test Engineer</t>
         </is>
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Shinkei</t>
         </is>
       </c>
       <c r="D390" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Manufacturing-Engineer/305827</t>
+          <t>https://careers.kula.ai/shinkei/50714-test-engineer</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="B391" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Developer Engineer</t>
+          <t>Manufacturing Engineer</t>
         </is>
       </c>
       <c r="C391" s="4" t="inlineStr">
@@ -12251,7 +12251,7 @@
       </c>
       <c r="D391" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Mechanical-Developer-Engineer/305746</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Manufacturing-Engineer/305827</t>
         </is>
       </c>
       <c r="E391" s="4" t="inlineStr">
@@ -12271,7 +12271,7 @@
       </c>
       <c r="B392" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Supervisor - Steam Turbine</t>
+          <t>Mechanical Developer Engineer</t>
         </is>
       </c>
       <c r="C392" s="2" t="inlineStr">
@@ -12281,7 +12281,7 @@
       </c>
       <c r="D392" s="3" t="inlineStr">
         <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Mechanical-Supervisor-Steam-Turbine/305697</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Mechanical-Developer-Engineer/305746</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="B393" s="4" t="inlineStr">
         <is>
-          <t>Quality Engineer</t>
+          <t>Mechanical Supervisor - Steam Turbine</t>
         </is>
       </c>
       <c r="C393" s="4" t="inlineStr">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="D393" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Quality-Engineer/305620</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Mechanical-Supervisor-Steam-Turbine/305697</t>
         </is>
       </c>
       <c r="E393" s="4" t="inlineStr">
@@ -12331,17 +12331,17 @@
       </c>
       <c r="B394" s="2" t="inlineStr">
         <is>
-          <t>Field Mechanical EngineerLas Vegas, NV • In office</t>
+          <t>Quality Engineer</t>
         </is>
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>The Boring Company</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="D394" s="3" t="inlineStr">
         <is>
-          <t>https://www.boringcompany.com/job/am9icG9zdDqNnDlV2dw0MRNMHiQTkTHB</t>
+          <t>https://jobs.siemens-energy.com/en_US/jobs/FolderDetail/Quality-Engineer/305620</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="B395" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing EngineerBastrop, TX • In office</t>
+          <t>Field Mechanical EngineerLas Vegas, NV • In office</t>
         </is>
       </c>
       <c r="C395" s="4" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="D395" s="5" t="inlineStr">
         <is>
-          <t>https://www.boringcompany.com/job/am9icG9zdDoXhmYElSmpAPXWkx0cUHIA</t>
+          <t>https://www.boringcompany.com/job/am9icG9zdDqNnDlV2dw0MRNMHiQTkTHB</t>
         </is>
       </c>
       <c r="E395" s="4" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="B396" s="2" t="inlineStr">
         <is>
-          <t>Mechanical EngineerBastrop, TX • In office</t>
+          <t>Manufacturing EngineerBastrop, TX • In office</t>
         </is>
       </c>
       <c r="C396" s="2" t="inlineStr">
@@ -12401,7 +12401,7 @@
       </c>
       <c r="D396" s="3" t="inlineStr">
         <is>
-          <t>https://www.boringcompany.com/job/am9icG9zdDr8pYtUm7z5M9rQRYIx383x</t>
+          <t>https://www.boringcompany.com/job/am9icG9zdDoXhmYElSmpAPXWkx0cUHIA</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
@@ -12421,7 +12421,7 @@
       </c>
       <c r="B397" s="4" t="inlineStr">
         <is>
-          <t>Mechanical EngineerDubai, UAE • In office</t>
+          <t>Mechanical EngineerBastrop, TX • In office</t>
         </is>
       </c>
       <c r="C397" s="4" t="inlineStr">
@@ -12431,7 +12431,7 @@
       </c>
       <c r="D397" s="5" t="inlineStr">
         <is>
-          <t>https://www.boringcompany.com/job/am9icG9zdDqHYUd752apxcA-uYMOpJ6Q</t>
+          <t>https://www.boringcompany.com/job/am9icG9zdDr8pYtUm7z5M9rQRYIx383x</t>
         </is>
       </c>
       <c r="E397" s="4" t="inlineStr">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Shop AssistantLas Vegas, NV • In office</t>
+          <t>Mechanical EngineerDubai, UAE • In office</t>
         </is>
       </c>
       <c r="C398" s="2" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="D398" s="3" t="inlineStr">
         <is>
-          <t>https://www.boringcompany.com/job/48e48c87-536a-458a-9b10-c8e2123376e2</t>
+          <t>https://www.boringcompany.com/job/am9icG9zdDqHYUd752apxcA-uYMOpJ6Q</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="B399" s="4" t="inlineStr">
         <is>
-          <t>Project EngineerBastrop, TX • In office</t>
+          <t>Mechanical Shop AssistantLas Vegas, NV • In office</t>
         </is>
       </c>
       <c r="C399" s="4" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="D399" s="5" t="inlineStr">
         <is>
-          <t>https://www.boringcompany.com/job/am9icG9zdDrXy777jdYdNi_n7fUtTR-p</t>
+          <t>https://www.boringcompany.com/job/48e48c87-536a-458a-9b10-c8e2123376e2</t>
         </is>
       </c>
       <c r="E399" s="4" t="inlineStr">
@@ -12511,7 +12511,7 @@
       </c>
       <c r="B400" s="2" t="inlineStr">
         <is>
-          <t>Senior Mechanical EngineerBastrop, TX • In office</t>
+          <t>Project EngineerBastrop, TX • In office</t>
         </is>
       </c>
       <c r="C400" s="2" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="D400" s="3" t="inlineStr">
         <is>
-          <t>https://www.boringcompany.com/job/am9icG9zdDq4K_o2kHceU4KGxcnKWHcn</t>
+          <t>https://www.boringcompany.com/job/am9icG9zdDrXy777jdYdNi_n7fUtTR-p</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="B401" s="4" t="inlineStr">
         <is>
-          <t>Structural EngineerDubai, UAE • In office</t>
+          <t>Senior Mechanical EngineerBastrop, TX • In office</t>
         </is>
       </c>
       <c r="C401" s="4" t="inlineStr">
@@ -12551,7 +12551,7 @@
       </c>
       <c r="D401" s="5" t="inlineStr">
         <is>
-          <t>https://www.boringcompany.com/job/am9icG9zdDpNbsEMmb3DN-QrDmS5Wc-w</t>
+          <t>https://www.boringcompany.com/job/am9icG9zdDq4K_o2kHceU4KGxcnKWHcn</t>
         </is>
       </c>
       <c r="E401" s="4" t="inlineStr">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t>Tunnel Design EngineerDubai, UAE • In office</t>
+          <t>Structural EngineerDubai, UAE • In office</t>
         </is>
       </c>
       <c r="C402" s="2" t="inlineStr">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="D402" s="3" t="inlineStr">
         <is>
-          <t>https://www.boringcompany.com/job/am9icG9zdDqOu214VaCudwmSOdV3XH2O</t>
+          <t>https://www.boringcompany.com/job/am9icG9zdDpNbsEMmb3DN-QrDmS5Wc-w</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="B403" s="4" t="inlineStr">
         <is>
-          <t>Tunnel Design EngineerLas Vegas, NV, Nashville, TN • In office</t>
+          <t>Tunnel Design EngineerDubai, UAE • In office</t>
         </is>
       </c>
       <c r="C403" s="4" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="D403" s="5" t="inlineStr">
         <is>
-          <t>https://www.boringcompany.com/job/am9icG9zdDpCfAbWObmXO9L7iWnTyraS</t>
+          <t>https://www.boringcompany.com/job/am9icG9zdDqOu214VaCudwmSOdV3XH2O</t>
         </is>
       </c>
       <c r="E403" s="4" t="inlineStr">
@@ -12631,17 +12631,17 @@
       </c>
       <c r="B404" s="2" t="inlineStr">
         <is>
-          <t>Manufacturing Engineer II</t>
+          <t>Tunnel Design EngineerLas Vegas, NV, Nashville, TN • In office</t>
         </is>
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>Vantedge Medical</t>
+          <t>The Boring Company</t>
         </is>
       </c>
       <c r="D404" s="3" t="inlineStr">
         <is>
-          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4523132</t>
+          <t>https://www.boringcompany.com/job/am9icG9zdDpCfAbWObmXO9L7iWnTyraS</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="B405" s="4" t="inlineStr">
         <is>
-          <t>Manufacturing R&amp;D Engineer</t>
+          <t>Manufacturing Engineer II</t>
         </is>
       </c>
       <c r="C405" s="4" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="D405" s="5" t="inlineStr">
         <is>
-          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4491013</t>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4523132</t>
         </is>
       </c>
       <c r="E405" s="4" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="B406" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Assembler I</t>
+          <t>Manufacturing R&amp;D Engineer</t>
         </is>
       </c>
       <c r="C406" s="2" t="inlineStr">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="D406" s="3" t="inlineStr">
         <is>
-          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4533107</t>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4491013</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="B407" s="4" t="inlineStr">
         <is>
-          <t>Mechanical Assembler II Temporary</t>
+          <t>Mechanical Assembler I</t>
         </is>
       </c>
       <c r="C407" s="4" t="inlineStr">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="D407" s="5" t="inlineStr">
         <is>
-          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4086861</t>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4533107</t>
         </is>
       </c>
       <c r="E407" s="4" t="inlineStr">
@@ -12751,7 +12751,7 @@
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Assembly Lead</t>
+          <t>Mechanical Assembler II Temporary</t>
         </is>
       </c>
       <c r="C408" s="2" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="D408" s="3" t="inlineStr">
         <is>
-          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4552436</t>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4086861</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
@@ -12781,32 +12781,62 @@
       </c>
       <c r="B409" s="4" t="inlineStr">
         <is>
+          <t>Mechanical Assembly Lead</t>
+        </is>
+      </c>
+      <c r="C409" s="4" t="inlineStr">
+        <is>
+          <t>Vantedge Medical</t>
+        </is>
+      </c>
+      <c r="D409" s="5" t="inlineStr">
+        <is>
+          <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4552436</t>
+        </is>
+      </c>
+      <c r="E409" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F409" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="2" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
           <t>Quality Engineer</t>
         </is>
       </c>
-      <c r="C409" s="4" t="inlineStr">
+      <c r="C410" s="2" t="inlineStr">
         <is>
           <t>Vantedge Medical</t>
         </is>
       </c>
-      <c r="D409" s="5" t="inlineStr">
+      <c r="D410" s="3" t="inlineStr">
         <is>
           <t>https://recruiting.paylocity.com/Recruiting/Jobs/Details/4488316</t>
         </is>
       </c>
-      <c r="E409" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F409" s="4" t="inlineStr">
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F409"/>
+  <autoFilter ref="A1:F410"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -13216,6 +13246,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D407" r:id="rId406"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D408" r:id="rId407"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D410" r:id="rId409"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13228,7 +13259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13427,12 +13458,12 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Marvin</t>
+          <t>Jordan &amp; Skala Engineers</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>https://careers-marvin.icims.com/jobs/search</t>
+          <t>https://www.jordanskala.com/careers/current-openings/</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -13442,7 +13473,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>HTTP 405 when loading https://careers-marvin.icims.com/jobs/search?searchSortField=postedDate&amp;searchSortDirection=desc&amp;pr=1</t>
+          <t>HTTP 504 when loading page 1 (https://www.jordanskala.com/careers/current-openings/)</t>
         </is>
       </c>
     </row>
@@ -13452,12 +13483,12 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Marvin</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>https://jobs.nokia.com/en/sites/CX_1/jobs</t>
+          <t>https://careers-marvin.icims.com/jobs/search</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
@@ -13467,7 +13498,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Bad/unreadable response from https://jobs.nokia.com/hcmRestApi/resources/latest/recruitingCEJobRequisitions (JSONDecodeError: Expecting value: line 1 column 1 (char 0)) (x9)</t>
+          <t>HTTP 405 when loading https://careers-marvin.icims.com/jobs/search?searchSortField=postedDate&amp;searchSortDirection=desc&amp;pr=1</t>
         </is>
       </c>
     </row>
@@ -13477,12 +13508,12 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Pelican Energy Consultants</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>https://www.pelicanenergy.com/careers-employment</t>
+          <t>https://jobs.nokia.com/en/sites/CX_1/jobs</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -13492,7 +13523,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Page loaded but its ADP job list never appeared (site layout may have changed)</t>
+          <t>Bad/unreadable response from https://jobs.nokia.com/hcmRestApi/resources/latest/recruitingCEJobRequisitions (JSONDecodeError: Expecting value: line 1 column 1 (char 0)) (x9)</t>
         </is>
       </c>
     </row>
@@ -13577,12 +13608,12 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Agility Robotics</t>
+          <t>Volvo Group</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>https://www.agilityrobotics.com/careers</t>
+          <t>https://jobs.volvogroup.com/?locale=en-EN</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
@@ -13602,86 +13633,36 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Dyno Nobel</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>https://efds.fa.em5.oraclecloud.com/hcmUI/CandidateExperience/en/sites/CX_1/jobs</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>Timed out</t>
+          <t>https://phh.tbe.taleo.net/phh02/ats/careers/v2/searchResults?org=DYNONOBEL&amp;cws=43</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Partial</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Did not finish within 180 seconds; jobs from this site may be missing.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Volvo Group</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>https://jobs.volvogroup.com/?locale=en-EN</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="inlineStr">
-        <is>
-          <t>Timed out</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Did not finish within 180 seconds; jobs from this site may be missing.</t>
+          <t>Page loaded but no job listings were found on it (site layout may have changed)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Dyno Nobel</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>https://phh.tbe.taleo.net/phh02/ats/careers/v2/searchResults?org=DYNONOBEL&amp;cws=43</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>Partial</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Page loaded but no job listings were found on it (site layout may have changed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>Failed = nothing could be read from the site. Partial = some pages/searches failed, so some jobs may be missing. Timed out = the site took too long and was skipped.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E17"/>
+  <autoFilter ref="A1:E15"/>
   <mergeCells count="1">
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
@@ -13698,8 +13679,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13711,7 +13690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -13735,21 +13714,21 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>New Postings Today: 408</t>
+          <t>New Postings Today: 409</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Companies: 39</t>
+          <t>Companies: 40</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Generated: 2026-10-29T04:35:45.393353</t>
+          <t>Generated: 2026-10-29T04:44:45.337540</t>
         </is>
       </c>
     </row>
@@ -13763,7 +13742,7 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>Websites with scan issues: 16 (see "Scan Issues" sheet)</t>
+          <t>Websites with scan issues: 14 (see "Scan Issues" sheet)</t>
         </is>
       </c>
     </row>
@@ -13869,107 +13848,107 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bosch</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Calista/Yulista</t>
+          <t>Bosch</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cummins</t>
+          <t>Calista/Yulista</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dana Inc</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EwingCole</t>
+          <t>Dana Inc</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Figure</t>
+          <t>EwingCole</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Formlabs</t>
+          <t>Figure</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Hargrove EPC</t>
+          <t>Formlabs</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Hendrickson</t>
+          <t>Hargrove EPC</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hyundai</t>
+          <t>Hendrickson</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Insulet</t>
+          <t>Hyundai</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -13979,21 +13958,21 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>JTEKT North America</t>
+          <t>Insulet</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jordan &amp; Skala Engineers</t>
+          <t>JTEKT North America</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33">
@@ -14069,110 +14048,120 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Quantum Computing Inc</t>
+          <t>Pelican Energy Consultants</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Schaeffler</t>
+          <t>Quantum Computing Inc</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Scout Motors</t>
+          <t>Schaeffler</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Shinkei</t>
+          <t>Scout Motors</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Shinkei</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Taylor</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Tenneco</t>
+          <t>Taylor</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Terex</t>
+          <t>Tenneco</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>The Boring Company</t>
+          <t>Terex</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Vantedge Medical</t>
+          <t>The Boring Company</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>Vantedge Medical</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>Xylem</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B51" t="n">
         <v>4</v>
       </c>
     </row>
